--- a/forms/trg/Formulir_TRG_wildev.xlsx
+++ b/forms/trg/Formulir_TRG_wildev.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Risma Illa Maulany, S.Hut, M.Nat.ResSt, Ph.D.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -957,7 +961,11 @@
           <t>Andi Siady Hamzah, S.Hut, M.Si</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -998,7 +1006,11 @@
           <t>Arida Fauziyah, S.Si, M.Sc.</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1035,7 +1047,11 @@
           <t>Dr. Asrianny, S.Hut, M.Si</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1076,7 +1092,11 @@
           <t>Dr. Putu Supadma Putra, S.Hut.</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1113,7 +1133,11 @@
           <t>Ir. Nasri, S.Hut, M. Hut, IPU</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1154,7 +1178,11 @@
           <t>Prof. Dr. Ir. Amran Achmad, M.Sc</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1195,7 +1223,11 @@
           <t>Prof. Dr. Ir. Ngakan Putu Oka, M.Sc</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1236,7 +1268,11 @@
           <t>Wardiman Mas’ud, S.Hut., M.Hut</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1275,7 +1311,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1316,7 +1352,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1357,7 +1393,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1398,7 +1434,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1435,7 +1471,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1476,7 +1512,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1517,7 +1553,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1554,7 +1590,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1591,7 +1627,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1628,7 +1664,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
